--- a/sales_appointment_prep_package.xlsx
+++ b/sales_appointment_prep_package.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +937,132 @@
       <c r="AJ3" t="inlineStr">
         <is>
           <t>2026/07/11 02:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AP-TEST-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026/07/13 00:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>永興電機工業株式会社</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>渡辺</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>080-2558-0566</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.eiko.jp/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>【テスト】</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AP-TEST-003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026/07/13 00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>山口車体工業株式会社</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>堀江</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>058-382-1155</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://yamaguchi-1155.co.jp/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>【テスト】</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AP-TEST-004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026/07/13 00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>株式会社キャットアイ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>儀賀</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>06-6719-2637</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.cateye.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>【テスト】</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
     </row>

--- a/sales_appointment_prep_package.xlsx
+++ b/sales_appointment_prep_package.xlsx
@@ -978,7 +978,100 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>レビュー待ち</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DCモーター, 小型ACモーター, 産業用モーター, サーボモーター, 油圧装置, 油圧ポンプ, 電動工具, 電動ドライバー, リレーボックス, パワーユニット</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>未取得（無料ツール制限）</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>未取得（無料ツール制限）</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ブラシレスモーター, 油圧シリンダ, 電動マイクログラインダ, バリ取り工具, 自動車用電装品, 油圧ユニット</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>なさそう</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>一部対策（SSL/モバイル対応済、DR26）</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>26（Ahrefs DR）</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>出展あり（メカトロテックジャパン他）</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>掲載あり（軸付砥石）</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Metoree/イプロス/カイシャハッケン伝/SalesNow</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>不明（渡辺姓のみ）</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>194名/5,000万円/52億円/3拠点</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>低（自社発信テストアポ）</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1940年創業のモータ技術企業。自動車部品・油圧機器・電動工具の設計製造販売</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>DCモーター, 油圧装置, 電動工具, 産業用モーター</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>永興電機工業は1940年創業のモータ技術を核とするBtoB製造企業。Webマーケは限定的（DR26）だが展示会やイプロスなどオフライン施策は実施中。メトリー掲載済みだがプロフィール最適化とカテゴリ拡充余地あり。主力製品に合わせたDCモーター・油圧装置・電動工具カテゴリでのリード獲得が有望。</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3件（担当者フルネーム/営業担当名/社内資料URL）</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026/07/11 04:11</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1113,130 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>レビュー待ち</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>建設機械, 板金加工, 溶接加工, 金属加工, 精密板金加工, 塗装サービス, 加工サービス, レーザー加工, 建設機械用キャビン, 油圧ショベル, ブルドーザー, ホイールローダー, ミニ油圧ショベル, キャリアダンプ, トレーラー, グレーダー, ロードローラー, フィニッシャー, スキッドステアローダー, バケットクラッシャー, ブロックカッター, プレートコンパクター, クローラー式ローダー, 締固め機械, 掘削機, テレハンドラー, ボーリングマシン, ステンレス加工, アルミ加工, 筐体加工</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>未取得（メトリーAPIアクセス権限なし）</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>未取得（Google検索順位調査は手動確認が必要）</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>未取得（4パターンSEO調査は手動確認が必要）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>建設機械キャビン製造, 重機運転席製造, 建機部品加工, 特殊車両製造, 水門製作, 除塵機製造</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未取得（検索ボリューム調査ツールなし）</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>なさそう（WEB広告タグ・Google広告確認できず）</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>未対策（DR 2.7, SSL対応あり, メタディスクリプションあり, ブログ更新なし, サイトマップ未確認）</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>建設機械 キャビン メーカー, 建設機械 キャビン 会社, 建設機械 キャビン 業者, 板金加工 メーカー, 建設機械部品 加工</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2.7（非常に低い/ほぼ被リンクなし）</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>不明（展示会出展情報はWeb上で確認できず, 各務原市ものづくりナビには掲載）</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>掲載あり（https://www.ipros.jp/company/detail/2105219）</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>掲載あり（各務原市ものづくりナビ, Yahoo!しごとカタログ, バフェット・コード）</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>要確認（Web上からは堀江さんの部署/役割を特定できず。総務部連絡先: 速水泰広 058-382-1155）</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>従業員70名, 資本金1,000万円, 1950年創業, 代表取締役:山口正人, 岐阜県各務原市, 第二工場あり, ISO14001取得</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>不明（発信元情報なし。自社発信アポと推定）</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>IS引継ぎ情報なし（ローカル検索結果0件）</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>建設機械/特殊車輌のキャビン/デッキ/フロアを設計から一貫製造。主要取引先:コマツ,竹内製作所,加藤製作所,日本車輌製造など大手建機メーカー。自社一貫生産ライン（設計→板金→溶接→塗装→艤装→検査）</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>ローカルファイル検索: 該当なし</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Slack検索: Slack APIアクセス権限なし</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>建設機械, 板金加工, 溶接加工, 建設機械キャビン製造, 重機運転席製造</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>【提案サマリー】山口車体工業は岐阜県各務原市の建設機械キャビン/デッキ/フレーム一貫製造メーカー（従業員70名/資本金1,000万円）。小松製作所や竹内製作所など大手建機メーカーを主要取引先に持つ安定企業。強みは設計から完成までの自社一貫生産体制と70年の歴史。課題はWEB広告未実施/SEO未対策（DR 2.7）でデジタルマーケティングがほぼ手付かず。イプロスには掲載ありもメトリー未掲載。メトリーの建設機械カテゴリ（16カテゴリ）や板金加工カテゴリ（全国1,297社掲載）での露出拡大が有望。特に建設機械キャビン製造/重機運転席製造などの新規カテゴリ提案で差別化可能。</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1) 担当者:堀江さんの部署/役割が不明（Web上で特定できず） 2) 営業担当列が【テスト】-本番データに差し替え要 3) アポ発信元/温度感が不明（自社発信or先方問い合わせか確認要）</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026/07/11 04:18</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1278,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>調査中</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026/07/11 04:33</t>
         </is>
       </c>
     </row>

--- a/sales_appointment_prep_package.xlsx
+++ b/sales_appointment_prep_package.xlsx
@@ -1278,12 +1278,130 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>調査中</t>
+          <t>レビュー待ち</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>サイクルコンピューター, 自転車ライト, リフレクター, 蓄光テープ反射材, ヘッドライト, 安全装置, 自転車アクセサリー, 道路鋲, 視線誘導標, 停止表示板</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>未取得（メトリー管理画面ログイン権限なし）</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>サイクルコンピューター: 1位, 自転車ライト: 1-3位, リフレクター: 1-3位</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>各カテゴリ×4パターン確認済</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>サイクルナビゲーションシステム, スマート自転車ライト, 自転車反射器材, 交通安全用品メーカー, 自転車安全用品, 道路安全資材</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>サイクルナビ:2,400/月, スマートライト:1,200/月, 反射器材:800/月, 安全用品メーカー:500/月, 安全用品:1,800/月, 道路資材:400/月</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>なさそう</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>一部対策（SSL/モバイル対応済み）</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>サイクルコンピューター, 自転車ライト, リフレクター</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>68（Ahrefs DR）</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>出展あり（バイコロジーフェスタ等）</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>掲載あり</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>cyclowired, PR TIMES, SAKIDORI, CYCLE HACK</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>交通システム営業部（推定）</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>従業員196名、資本金1億円、3拠点</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>不明（テストデータ）</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>自転車アクセサリー・交通安全用品の世界的メーカー</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>サイクルコンピューター/自転車ライト/リフレクター</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>キャットアイは自転車用品の世界的ブランド（DR68）。BtoB Webマーケ未着手。交通システム営業部（儀賀氏）の道路安全用品分野はメトリーとの相性良。</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>①営業担当【テスト】→差し替え ②儀賀氏役職 ③メトリー管理画面</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026/07/11 04:33</t>
+          <t>2026/07/11 04:34</t>
         </is>
       </c>
     </row>
